--- a/case_studies/high_feedstock_availability_10_dd/2030/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_10_dd/2030/technologies.xlsx
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
@@ -970,10 +970,10 @@
         <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1167,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>653.27</v>
+        <v>357.76</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>653.27</v>
